--- a/Prueba-01-Analisis-Datos/solucion.xlsx
+++ b/Prueba-01-Analisis-Datos/solucion.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="620" yWindow="460" windowWidth="23880" windowHeight="17540" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="620" yWindow="460" windowWidth="25420" windowHeight="17540" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Material de apoyo - Prueba " sheetId="7" r:id="rId1"/>
@@ -2290,14 +2290,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2367,8 +2360,23 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2397,12 +2405,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
     <fill>
@@ -2437,12 +2439,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
         <bgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor rgb="FF0066CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor rgb="FF008080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2525,48 +2551,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2581,93 +2630,81 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2676,29 +2713,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -2818,7 +2881,13 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2892,15 +2961,25 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
@@ -2970,7 +3049,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.120813059391049"/>
+          <c:y val="0.148002797842928"/>
+          <c:w val="0.857937557768274"/>
+          <c:h val="0.682636479510186"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -3111,11 +3200,11 @@
         </c:hiLowLines>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="-2110576160"/>
-        <c:axId val="-2110570336"/>
+        <c:axId val="2118874912"/>
+        <c:axId val="2118880960"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-2110576160"/>
+        <c:axId val="2118874912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3147,7 +3236,14 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.511457725788984"/>
+              <c:y val="0.916541198981015"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3183,7 +3279,7 @@
             <a:endParaRPr lang="es-ES_tradnl"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-2110570336"/>
+        <c:crossAx val="2118880960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3191,7 +3287,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-2110570336"/>
+        <c:axId val="2118880960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3231,7 +3327,14 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.0177078190338976"/>
+              <c:y val="0.397593017216757"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3267,7 +3370,7 @@
             <a:endParaRPr lang="es-ES_tradnl"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-2110576160"/>
+        <c:crossAx val="2118874912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="4000.0"/>
@@ -3282,7 +3385,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.727959795721484"/>
+          <c:y val="0.346333880229536"/>
+          <c:w val="0.174478626732142"/>
+          <c:h val="0.0619532710115713"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10761,1550 +10873,1550 @@
   <dimension ref="A1:CU1397"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="59"/>
-    <col min="2" max="2" width="17.33203125" style="51" customWidth="1"/>
-    <col min="3" max="3" width="23" style="51" customWidth="1"/>
-    <col min="4" max="4" width="25" style="51" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" style="51" customWidth="1"/>
-    <col min="6" max="99" width="10.83203125" style="59"/>
-    <col min="100" max="16384" width="10.83203125" style="51"/>
+    <col min="1" max="1" width="10.83203125" style="53"/>
+    <col min="2" max="2" width="17.33203125" style="46" customWidth="1"/>
+    <col min="3" max="3" width="30.5" style="46" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" style="46" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" style="46" customWidth="1"/>
+    <col min="6" max="99" width="10.83203125" style="53"/>
+    <col min="100" max="16384" width="10.83203125" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:5" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="60" t="s">
+    <row r="1" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:5" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="54" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="3" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="62" t="s">
         <v>650</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="62" t="s">
         <v>652</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="62" t="s">
         <v>654</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="62" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="B5" s="53" t="s">
+    <row r="5" spans="2:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="B5" s="48" t="s">
         <v>655</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="47" t="s">
         <v>656</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="47" t="s">
         <v>657</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="46" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="B6" s="53" t="s">
+    <row r="6" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B6" s="48" t="s">
         <v>658</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="49" t="s">
         <v>659</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="47" t="s">
         <v>660</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="47" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="B7" s="53" t="s">
+    <row r="7" spans="2:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="B7" s="48" t="s">
         <v>662</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="46" t="s">
         <v>663</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="47" t="s">
         <v>664</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="47" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="B8" s="53" t="s">
+    <row r="8" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B8" s="48" t="s">
         <v>665</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="46" t="s">
         <v>666</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="47" t="s">
         <v>667</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="46" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="9" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="2:5" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="60" t="s">
+    <row r="9" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="2:5" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="54" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="12" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="61" t="s">
         <v>670</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="61" t="s">
         <v>671</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="61" t="s">
         <v>672</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="61" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="B14" s="56">
+    <row r="14" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B14" s="50">
         <v>1</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="51" t="s">
         <v>673</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="52" t="s">
         <v>684</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="51" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="B15" s="56">
+    <row r="15" spans="2:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="B15" s="50">
         <v>2</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="51" t="s">
         <v>675</v>
       </c>
-      <c r="D15" s="58" t="s">
+      <c r="D15" s="52" t="s">
         <v>676</v>
       </c>
-      <c r="E15" s="57" t="s">
+      <c r="E15" s="51" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="B16" s="56">
+    <row r="16" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B16" s="50">
         <v>3</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="51" t="s">
         <v>678</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="52" t="s">
         <v>679</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E16" s="51" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="B17" s="56">
+    <row r="17" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B17" s="50">
         <v>4</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="51" t="s">
         <v>681</v>
       </c>
-      <c r="D17" s="58" t="s">
+      <c r="D17" s="52" t="s">
         <v>682</v>
       </c>
-      <c r="E17" s="57" t="s">
+      <c r="E17" s="51" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="18" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:5" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="33" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="36" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="54" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="63" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="129" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="130" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="131" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="132" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="133" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="134" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="135" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="136" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="137" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="138" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="139" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="140" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="141" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="142" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="143" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="144" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="145" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="146" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="147" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="148" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="149" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="150" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="151" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="152" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="153" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="154" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="155" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="156" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="157" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="158" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="159" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="160" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="161" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="162" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="163" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="164" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="165" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="166" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="167" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="168" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="169" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="170" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="171" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="172" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="173" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="174" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="175" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="176" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="177" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="178" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="179" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="180" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="181" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="182" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="183" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="184" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="185" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="186" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="187" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="188" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="189" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="190" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="191" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="192" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="193" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="194" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="195" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="196" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="197" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="198" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="199" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="200" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="201" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="202" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="203" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="204" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="205" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="206" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="207" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="208" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="209" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="210" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="211" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="212" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="213" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="214" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="215" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="216" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="217" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="218" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="219" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="220" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="221" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="222" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="223" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="224" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="225" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="226" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="227" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="228" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="229" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="230" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="231" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="232" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="233" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="234" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="235" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="236" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="237" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="238" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="239" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="240" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="241" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="242" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="243" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="244" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="245" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="246" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="247" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="248" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="249" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="250" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="251" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="252" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="253" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="254" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="255" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="256" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="257" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="258" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="259" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="260" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="261" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="262" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="263" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="264" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="265" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="266" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="267" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="268" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="269" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="270" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="271" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="272" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="273" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="274" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="275" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="276" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="277" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="278" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="279" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="280" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="281" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="282" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="283" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="284" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="285" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="286" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="287" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="288" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="289" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="290" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="291" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="292" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="293" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="294" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="295" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="296" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="297" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="298" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="299" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="300" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="301" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="302" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="303" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="304" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="305" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="306" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="307" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="308" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="309" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="310" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="311" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="312" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="313" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="314" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="315" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="316" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="317" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="318" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="319" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="320" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="321" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="322" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="323" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="324" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="325" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="326" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="327" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="328" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="329" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="330" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="331" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="332" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="333" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="334" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="335" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="336" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="337" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="338" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="339" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="340" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="341" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="342" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="343" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="344" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="345" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="346" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="347" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="348" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="349" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="350" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="351" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="352" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="353" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="354" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="355" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="356" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="357" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="358" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="359" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="360" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="361" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="362" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="363" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="364" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="365" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="366" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="367" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="368" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="369" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="370" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="371" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="372" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="373" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="374" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="375" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="376" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="377" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="378" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="379" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="380" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="381" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="382" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="383" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="384" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="385" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="386" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="387" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="388" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="389" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="390" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="391" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="392" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="393" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="394" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="395" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="396" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="397" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="398" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="399" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="400" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="401" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="402" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="403" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="404" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="405" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="406" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="407" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="408" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="409" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="410" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="411" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="412" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="413" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="414" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="415" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="416" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="417" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="418" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="419" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="420" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="421" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="422" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="423" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="424" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="425" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="426" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="427" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="428" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="429" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="430" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="431" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="432" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="433" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="434" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="435" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="436" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="437" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="438" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="439" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="440" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="441" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="442" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="443" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="444" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="445" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="446" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="447" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="448" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="449" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="450" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="451" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="452" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="453" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="454" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="455" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="456" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="457" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="458" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="459" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="460" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="461" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="462" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="463" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="464" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="465" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="466" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="467" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="468" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="469" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="470" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="471" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="472" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="473" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="474" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="475" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="476" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="477" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="478" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="479" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="480" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="481" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="482" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="483" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="484" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="485" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="486" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="487" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="488" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="489" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="490" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="491" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="492" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="493" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="494" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="495" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="496" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="497" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="498" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="499" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="500" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="501" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="502" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="503" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="504" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="505" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="506" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="507" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="508" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="509" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="510" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="511" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="512" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="513" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="514" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="515" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="516" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="517" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="518" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="519" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="520" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="521" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="522" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="523" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="524" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="525" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="526" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="527" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="528" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="529" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="530" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="531" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="532" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="533" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="534" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="535" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="536" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="537" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="538" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="539" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="540" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="541" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="542" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="543" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="544" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="545" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="546" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="547" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="548" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="549" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="550" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="551" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="552" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="553" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="554" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="555" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="556" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="557" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="558" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="559" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="560" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="561" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="562" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="563" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="564" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="565" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="566" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="567" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="568" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="569" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="570" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="571" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="572" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="573" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="574" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="575" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="576" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="577" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="578" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="579" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="580" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="581" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="582" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="583" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="584" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="585" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="586" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="587" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="588" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="589" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="590" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="591" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="592" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="593" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="594" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="595" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="596" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="597" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="598" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="599" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="600" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="601" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="602" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="603" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="604" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="605" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="606" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="607" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="608" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="609" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="610" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="611" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="612" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="613" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="614" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="615" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="616" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="617" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="618" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="619" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="620" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="621" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="622" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="623" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="624" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="625" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="626" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="627" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="628" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="629" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="630" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="631" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="632" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="633" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="634" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="635" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="636" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="637" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="638" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="639" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="640" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="641" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="642" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="643" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="644" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="645" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="646" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="647" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="648" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="649" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="650" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="651" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="652" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="653" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="654" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="655" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="656" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="657" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="658" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="659" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="660" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="661" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="662" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="663" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="664" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="665" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="666" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="667" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="668" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="669" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="670" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="671" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="672" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="673" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="674" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="675" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="676" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="677" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="678" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="679" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="680" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="681" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="682" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="683" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="684" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="685" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="686" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="687" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="688" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="689" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="690" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="691" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="692" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="693" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="694" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="695" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="696" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="697" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="698" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="699" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="700" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="701" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="702" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="703" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="704" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="705" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="706" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="707" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="708" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="709" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="710" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="711" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="712" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="713" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="714" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="715" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="716" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="717" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="718" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="719" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="720" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="721" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="722" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="723" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="724" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="725" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="726" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="727" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="728" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="729" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="730" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="731" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="732" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="733" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="734" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="735" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="736" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="737" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="738" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="739" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="740" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="741" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="742" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="743" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="744" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="745" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="746" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="747" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="748" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="749" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="750" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="751" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="752" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="753" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="754" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="755" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="756" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="757" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="758" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="759" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="760" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="761" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="762" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="763" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="764" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="765" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="766" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="767" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="768" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="769" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="770" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="771" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="772" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="773" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="774" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="775" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="776" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="777" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="778" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="779" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="780" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="781" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="782" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="783" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="784" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="785" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="786" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="787" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="788" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="789" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="790" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="791" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="792" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="793" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="794" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="795" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="796" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="797" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="798" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="799" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="800" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="801" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="802" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="803" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="804" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="805" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="806" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="807" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="808" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="809" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="810" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="811" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="812" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="813" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="814" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="815" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="816" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="817" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="818" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="819" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="820" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="821" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="822" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="823" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="824" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="825" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="826" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="827" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="828" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="829" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="830" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="831" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="832" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="833" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="834" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="835" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="836" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="837" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="838" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="839" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="840" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="841" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="842" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="843" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="844" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="845" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="846" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="847" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="848" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="849" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="850" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="851" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="852" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="853" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="854" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="855" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="856" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="857" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="858" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="859" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="860" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="861" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="862" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="863" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="864" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="865" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="866" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="867" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="868" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="869" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="870" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="871" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="872" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="873" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="874" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="875" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="876" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="877" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="878" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="879" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="880" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="881" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="882" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="883" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="884" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="885" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="886" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="887" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="888" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="889" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="890" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="891" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="892" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="893" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="894" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="895" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="896" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="897" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="898" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="899" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="900" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="901" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="902" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="903" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="904" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="905" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="906" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="907" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="908" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="909" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="910" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="911" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="912" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="913" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="914" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="915" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="916" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="917" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="918" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="919" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="920" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="921" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="922" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="923" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="924" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="925" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="926" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="927" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="928" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="929" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="930" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="931" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="932" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="933" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="934" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="935" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="936" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="937" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="938" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="939" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="940" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="941" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="942" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="943" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="944" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="945" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="946" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="947" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="948" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="949" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="950" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="951" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="952" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="953" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="954" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="955" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="956" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="957" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="958" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="959" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="960" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="961" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="962" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="963" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="964" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="965" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="966" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="967" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="968" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="969" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="970" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="971" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="972" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="973" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="974" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="975" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="976" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="977" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="978" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="979" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="980" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="981" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="982" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="983" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="984" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="985" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="986" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="987" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="988" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="989" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="990" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="991" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="992" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="993" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="994" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="995" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="996" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="997" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="998" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="999" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1005" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1006" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1007" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1008" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1009" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1010" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1011" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1012" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1013" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1014" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1015" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1016" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1017" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1018" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1019" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1020" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1021" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1022" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1023" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1024" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1025" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1026" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1027" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1028" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1029" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1030" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1031" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1032" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1033" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1034" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1035" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1036" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1037" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1038" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1039" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1040" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1041" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1042" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1043" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1044" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1045" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1046" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1047" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1048" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1049" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1050" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1051" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1052" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1053" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1054" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1055" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1056" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1057" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1058" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1059" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1060" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1061" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1062" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1063" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1064" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1065" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1066" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1067" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1068" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1069" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1070" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1071" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1072" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1073" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1074" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1075" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1076" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1077" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1078" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1079" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1080" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1081" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1082" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1083" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1084" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1085" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1086" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1087" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1088" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1089" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1090" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1091" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1092" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1093" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1094" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1095" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1096" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1097" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1098" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1099" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1100" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1101" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1102" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1103" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1104" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1105" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1106" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1107" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1108" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1109" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1110" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1111" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1112" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1113" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1114" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1115" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1116" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1117" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1118" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1119" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1120" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1121" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1122" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1123" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1124" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1125" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1126" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1127" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1128" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1129" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1130" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1131" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1132" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1133" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1134" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1135" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1136" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1137" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1138" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1139" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1140" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1141" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1142" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1143" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1144" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1145" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1146" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1147" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1148" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1149" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1150" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1151" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1152" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1153" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1154" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1155" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1156" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1157" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1158" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1159" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1160" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1161" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1162" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1163" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1164" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1165" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1166" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1167" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1168" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1169" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1170" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1171" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1172" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1173" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1174" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1175" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1176" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1177" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1178" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1179" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1180" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1181" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1182" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1183" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1184" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1185" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1186" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1187" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1188" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1189" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1190" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1191" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1192" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1193" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1194" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1195" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1196" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1197" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1198" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1199" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1200" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1201" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1202" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1203" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1204" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1205" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1206" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1207" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1208" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1209" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1210" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1211" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1212" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1213" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1214" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1215" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1216" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1217" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1218" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1219" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1220" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1221" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1222" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1223" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1224" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1225" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1226" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1227" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1228" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1229" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1230" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1231" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1232" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1233" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1234" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1235" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1236" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1237" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1238" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1239" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1240" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1241" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1242" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1243" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1244" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1245" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1246" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1247" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1248" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1249" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1250" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1251" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1252" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1253" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1254" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1255" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1256" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1257" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1258" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1259" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1260" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1261" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1262" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1263" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1264" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1265" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1266" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1267" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1268" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1269" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1270" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1271" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1272" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1273" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1274" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1275" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1276" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1277" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1278" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1279" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1280" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1281" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1282" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1283" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1284" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1285" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1286" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1287" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1288" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1289" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1290" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1291" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1292" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1293" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1294" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1295" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1296" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1297" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1298" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1299" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1300" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1301" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1302" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1303" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1304" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1305" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1306" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1307" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1308" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1309" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1310" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1311" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1312" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1313" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1314" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1315" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1316" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1317" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1318" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1319" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1320" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1321" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1322" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1323" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1324" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1325" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1326" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1327" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1328" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1329" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1330" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1331" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1332" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1333" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1334" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1335" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1336" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1337" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1338" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1339" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1340" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1341" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1342" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1343" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1344" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1345" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1346" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1347" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1348" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1349" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1350" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1351" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1352" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1353" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1354" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1355" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1356" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1357" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1358" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1359" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1360" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1361" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1362" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1363" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1364" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1365" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1366" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1367" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1368" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1369" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1370" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1371" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1372" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1373" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1374" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1375" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1376" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1377" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1378" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1379" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1380" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1381" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1382" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1383" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1384" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1385" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1386" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1387" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1388" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1389" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1390" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1391" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1392" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1393" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1394" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1395" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1396" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="1397" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="33" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="35" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="52" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="53" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="56" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="57" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="58" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="59" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="60" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="63" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="177" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="178" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="179" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="180" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="181" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="182" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="183" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="184" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="185" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="186" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="187" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="188" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="189" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="190" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="191" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="192" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="193" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="194" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="195" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="196" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="197" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="198" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="199" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="200" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="201" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="202" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="203" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="204" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="205" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="206" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="207" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="208" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="209" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="210" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="211" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="212" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="213" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="214" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="215" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="216" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="217" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="218" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="219" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="220" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="221" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="222" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="223" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="224" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="225" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="226" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="227" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="228" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="229" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="230" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="231" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="232" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="233" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="234" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="235" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="236" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="237" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="238" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="239" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="240" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="241" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="242" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="243" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="244" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="245" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="246" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="247" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="248" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="249" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="250" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="251" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="252" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="253" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="254" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="255" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="256" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="257" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="258" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="259" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="260" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="261" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="262" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="263" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="264" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="265" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="266" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="267" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="268" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="269" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="270" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="271" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="272" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="273" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="274" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="275" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="276" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="277" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="278" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="279" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="280" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="281" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="282" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="283" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="284" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="285" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="286" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="287" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="288" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="289" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="290" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="291" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="292" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="293" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="294" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="295" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="296" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="297" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="298" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="299" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="300" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="301" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="302" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="303" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="304" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="305" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="306" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="307" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="308" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="309" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="310" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="311" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="312" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="313" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="314" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="315" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="316" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="317" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="318" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="319" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="320" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="321" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="322" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="323" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="324" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="325" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="326" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="327" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="328" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="329" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="330" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="331" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="332" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="333" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="334" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="335" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="336" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="337" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="338" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="339" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="340" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="341" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="342" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="343" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="344" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="345" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="346" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="347" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="348" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="349" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="350" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="351" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="352" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="353" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="354" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="355" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="356" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="357" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="358" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="359" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="360" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="361" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="362" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="363" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="364" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="365" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="366" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="367" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="368" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="369" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="370" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="371" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="372" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="373" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="374" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="375" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="376" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="377" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="378" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="379" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="380" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="381" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="382" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="383" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="384" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="385" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="386" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="387" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="388" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="389" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="390" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="391" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="392" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="393" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="394" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="395" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="396" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="397" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="398" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="399" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="400" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="401" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="402" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="403" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="404" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="405" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="406" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="407" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="408" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="409" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="410" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="411" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="412" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="413" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="414" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="415" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="416" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="417" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="418" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="419" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="420" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="421" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="422" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="423" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="424" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="425" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="426" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="427" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="428" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="429" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="430" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="431" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="432" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="433" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="434" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="435" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="436" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="437" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="438" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="439" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="440" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="441" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="442" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="443" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="444" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="445" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="446" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="447" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="448" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="449" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="450" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="451" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="452" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="453" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="454" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="455" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="456" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="457" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="458" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="459" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="460" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="461" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="462" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="463" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="464" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="465" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="466" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="467" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="468" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="469" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="470" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="471" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="472" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="473" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="474" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="475" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="476" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="477" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="478" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="479" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="480" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="481" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="482" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="483" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="484" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="485" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="486" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="487" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="488" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="489" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="490" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="491" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="492" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="493" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="494" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="495" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="496" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="497" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="498" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="499" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="500" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="501" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="502" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="503" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="504" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="505" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="506" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="507" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="508" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="509" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="510" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="511" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="512" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="513" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="514" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="515" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="516" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="517" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="518" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="519" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="520" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="521" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="522" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="523" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="524" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="525" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="526" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="527" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="528" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="529" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="530" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="531" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="532" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="533" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="534" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="535" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="536" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="537" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="538" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="539" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="540" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="541" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="542" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="543" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="544" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="545" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="546" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="547" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="548" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="549" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="550" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="551" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="552" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="553" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="554" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="555" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="556" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="557" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="558" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="559" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="560" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="561" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="562" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="563" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="564" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="565" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="566" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="567" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="568" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="569" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="570" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="571" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="572" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="573" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="574" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="575" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="576" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="577" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="578" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="579" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="580" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="581" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="582" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="583" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="584" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="585" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="586" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="587" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="588" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="589" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="590" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="591" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="592" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="593" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="594" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="595" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="596" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="597" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="598" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="599" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="600" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="601" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="602" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="603" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="604" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="605" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="606" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="607" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="608" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="609" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="610" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="611" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="612" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="613" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="614" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="615" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="616" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="617" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="618" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="619" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="620" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="621" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="622" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="623" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="624" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="625" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="626" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="627" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="628" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="629" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="630" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="631" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="632" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="633" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="634" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="635" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="636" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="637" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="638" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="639" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="640" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="641" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="642" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="643" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="644" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="645" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="646" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="647" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="648" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="649" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="650" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="651" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="652" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="653" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="654" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="655" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="656" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="657" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="658" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="659" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="660" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="661" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="662" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="663" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="664" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="665" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="666" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="667" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="668" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="669" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="670" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="671" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="672" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="673" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="674" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="675" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="676" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="677" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="678" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="679" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="680" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="681" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="682" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="683" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="684" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="685" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="686" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="687" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="688" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="689" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="690" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="691" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="692" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="693" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="694" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="695" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="696" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="697" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="698" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="699" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="700" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="701" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="702" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="703" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="704" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="705" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="706" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="707" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="708" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="709" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="710" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="711" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="712" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="713" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="714" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="715" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="716" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="717" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="718" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="719" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="720" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="721" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="722" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="723" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="724" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="725" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="726" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="727" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="728" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="729" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="730" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="731" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="732" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="733" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="734" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="735" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="736" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="737" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="738" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="739" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="740" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="741" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="742" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="743" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="744" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="745" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="746" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="747" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="748" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="749" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="750" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="751" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="752" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="753" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="754" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="755" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="756" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="757" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="758" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="759" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="760" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="761" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="762" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="763" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="764" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="765" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="766" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="767" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="768" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="769" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="770" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="771" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="772" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="773" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="774" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="775" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="776" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="777" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="778" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="779" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="780" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="781" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="782" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="783" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="784" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="785" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="786" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="787" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="788" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="789" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="790" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="791" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="792" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="793" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="794" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="795" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="796" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="797" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="798" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="799" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="800" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="801" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="802" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="803" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="804" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="805" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="806" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="807" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="808" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="809" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="810" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="811" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="812" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="813" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="814" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="815" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="816" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="817" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="818" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="819" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="820" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="821" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="822" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="823" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="824" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="825" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="826" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="827" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="828" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="829" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="830" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="831" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="832" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="833" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="834" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="835" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="836" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="837" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="838" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="839" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="840" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="841" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="842" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="843" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="844" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="845" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="846" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="847" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="848" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="849" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="850" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="851" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="852" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="853" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="854" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="855" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="856" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="857" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="858" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="859" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="860" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="861" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="862" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="863" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="864" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="865" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="866" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="867" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="868" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="869" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="870" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="871" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="872" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="873" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="874" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="875" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="876" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="877" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="878" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="879" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="880" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="881" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="882" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="883" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="884" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="885" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="886" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="887" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="888" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="889" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="890" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="891" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="892" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="893" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="894" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="895" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="896" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="897" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="898" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="899" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="900" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="901" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="902" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="903" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="904" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="905" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="906" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="907" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="908" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="909" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="910" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="911" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="912" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="913" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="914" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="915" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="916" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="917" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="918" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="919" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="920" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="921" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="922" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="923" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="924" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="925" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="926" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="927" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="928" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="929" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="930" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="931" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="932" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="933" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="934" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="935" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="936" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="937" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="938" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="939" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="940" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="941" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="942" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="943" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="944" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="945" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="946" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="947" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="948" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="949" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="950" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="951" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="952" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="953" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="954" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="955" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="956" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="957" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="958" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="959" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="960" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="961" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="962" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="963" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="964" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="965" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="966" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="967" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="968" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="969" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="970" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="971" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="972" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="973" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="974" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="975" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="976" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="977" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="978" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="979" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="980" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="981" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="982" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="983" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="984" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="985" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="986" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="987" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="988" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="989" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="990" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="991" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="992" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="993" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="994" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="995" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="996" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="997" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="998" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="999" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1005" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1006" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1007" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1008" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1009" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1010" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1011" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1012" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1013" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1014" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1015" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1016" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1017" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1018" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1019" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1020" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1021" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1022" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1023" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1024" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1025" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1026" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1027" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1028" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1029" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1030" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1031" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1032" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1033" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1034" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1035" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1036" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1037" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1038" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1039" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1040" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1041" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1042" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1043" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1044" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1045" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1046" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1047" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1048" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1049" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1050" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1051" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1052" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1053" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1054" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1055" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1056" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1057" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1058" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1059" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1060" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1061" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1062" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1063" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1064" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1065" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1066" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1067" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1068" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1069" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1070" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1071" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1072" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1073" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1074" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1075" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1076" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1077" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1078" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1079" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1080" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1081" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1082" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1083" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1084" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1085" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1086" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1087" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1088" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1089" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1090" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1091" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1092" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1093" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1094" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1095" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1096" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1097" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1098" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1099" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1100" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1101" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1102" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1103" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1104" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1105" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1106" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1107" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1108" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1109" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1110" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1111" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1112" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1113" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1114" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1115" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1116" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1117" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1118" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1119" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1120" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1121" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1122" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1123" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1124" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1125" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1126" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1127" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1128" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1129" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1130" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1131" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1132" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1133" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1134" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1135" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1136" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1137" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1138" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1139" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1140" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1141" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1142" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1143" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1144" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1145" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1146" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1147" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1148" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1149" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1150" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1151" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1152" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1153" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1154" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1155" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1156" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1157" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1158" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1159" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1160" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1161" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1162" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1163" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1164" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1165" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1166" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1167" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1168" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1169" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1170" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1171" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1172" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1173" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1174" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1175" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1176" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1177" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1178" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1179" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1180" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1181" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1182" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1183" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1184" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1185" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1186" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1187" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1188" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1189" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1190" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1191" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1192" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1193" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1194" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1195" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1196" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1197" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1198" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1199" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1200" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1201" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1202" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1203" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1204" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1205" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1206" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1207" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1208" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1209" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1210" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1211" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1212" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1213" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1214" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1215" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1216" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1217" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1218" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1219" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1220" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1221" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1222" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1223" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1224" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1225" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1226" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1227" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1228" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1229" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1230" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1231" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1232" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1233" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1234" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1235" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1236" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1237" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1238" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1239" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1240" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1241" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1242" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1243" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1244" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1245" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1246" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1247" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1248" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1249" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1250" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1251" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1252" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1253" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1254" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1255" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1256" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1257" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1258" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1259" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1260" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1261" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1262" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1263" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1264" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1265" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1266" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1267" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1268" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1269" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1270" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1271" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1272" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1273" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1274" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1275" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1276" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1277" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1278" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1279" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1280" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1281" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1282" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1283" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1284" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1285" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1286" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1287" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1288" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1289" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1290" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1291" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1292" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1293" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1294" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1295" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1296" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1297" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1298" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1299" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1300" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1301" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1302" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1303" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1304" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1305" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1306" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1307" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1308" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1309" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1310" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1311" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1312" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1313" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1314" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1315" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1316" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1317" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1318" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1319" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1320" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1321" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1322" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1323" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1324" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1325" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1326" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1327" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1328" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1329" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1330" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1331" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1332" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1333" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1334" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1335" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1336" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1337" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1338" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1339" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1340" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1341" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1342" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1343" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1344" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1345" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1346" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1347" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1348" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1349" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1350" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1351" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1352" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1353" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1354" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1355" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1356" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1357" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1358" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1359" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1360" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1361" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1362" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1363" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1364" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1365" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1366" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1367" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1368" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1369" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1370" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1371" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1372" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1373" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1374" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1375" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1376" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1377" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1378" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1379" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1380" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1381" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1382" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1383" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1384" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1385" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1386" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1387" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1388" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1389" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1390" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1391" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1392" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1393" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1394" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1395" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1396" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1397" s="53" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -12319,17 +12431,19 @@
   <dimension ref="A2:AO67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20" style="1" customWidth="1"/>
-    <col min="4" max="7" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="10.83203125" style="60"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
     <col min="8" max="8" width="25.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="31.5" style="1" customWidth="1"/>
     <col min="10" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="2" t="s">
         <v>477</v>
       </c>
     </row>
@@ -12339,270 +12453,272 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+      <c r="B4" s="63" t="s">
         <v>444</v>
       </c>
-      <c r="B4" s="14"/>
+      <c r="C4" s="64"/>
     </row>
     <row r="5" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>447</v>
       </c>
-      <c r="B6" s="17">
+      <c r="C6" s="16">
         <v>12500</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="58" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>448</v>
       </c>
-      <c r="B7" s="19">
+      <c r="C7" s="18">
         <v>13200</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="19" t="s">
         <v>447</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="20">
         <v>12500</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="B8" s="17">
+      <c r="C8" s="16">
         <v>11800</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="21" t="s">
         <v>448</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="22">
         <v>13200</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B9" s="19">
+      <c r="C9" s="18">
         <v>14500</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="19" t="s">
         <v>449</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="20">
         <v>11800</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="B10" s="17">
+      <c r="C10" s="16">
         <v>15200</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="21" t="s">
         <v>450</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="22">
         <v>14500</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>452</v>
       </c>
-      <c r="B11" s="19">
+      <c r="C11" s="18">
         <v>14800</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="19" t="s">
         <v>451</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="20">
         <v>15200</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <v>14800</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="24" t="s">
+      <c r="B13" s="65" t="s">
         <v>453</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
     </row>
     <row r="14" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="25" t="s">
+      <c r="B15" s="23" t="s">
         <v>457</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="C15" s="24" t="s">
         <v>458</v>
       </c>
-      <c r="C15" s="27">
-        <f>AVERAGE(B6:B11)</f>
+      <c r="D15" s="25">
+        <f>AVERAGE(C6:C11)</f>
         <v>13666.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="B16" s="26" t="s">
         <v>459</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="C16" s="27" t="s">
         <v>460</v>
       </c>
-      <c r="C16" s="30">
-        <f>MEDIAN(B6:B11)</f>
+      <c r="D16" s="28">
+        <f>MEDIAN(C6:C11)</f>
         <v>13850</v>
       </c>
     </row>
     <row r="17" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
+      <c r="B17" s="23" t="s">
         <v>461</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="24" t="s">
         <v>462</v>
       </c>
-      <c r="C17" s="27">
-        <f>STDEV(B6:B11)</f>
+      <c r="D17" s="25">
+        <f>STDEV(C6:C11)</f>
         <v>1370.6446172026747</v>
       </c>
     </row>
     <row r="18" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
+      <c r="B18" s="26" t="s">
         <v>463</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="C18" s="27" t="s">
         <v>464</v>
       </c>
-      <c r="C18" s="30">
-        <f>VAR(B6:B11)</f>
+      <c r="D18" s="28">
+        <f>VAR(C6:C11)</f>
         <v>1878666.6666666665</v>
       </c>
     </row>
     <row r="19" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="25" t="s">
+      <c r="B19" s="23" t="s">
         <v>465</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="C19" s="24" t="s">
         <v>466</v>
       </c>
-      <c r="C19" s="27">
-        <f>MIN(B6:B11)</f>
+      <c r="D19" s="25">
+        <f>MIN(C6:C11)</f>
         <v>11800</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
+      <c r="B20" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="C20" s="27" t="s">
         <v>468</v>
       </c>
-      <c r="C20" s="30">
-        <f>MAX(B6:B11)</f>
+      <c r="D20" s="28">
+        <f>MAX(C6:C11)</f>
         <v>15200</v>
       </c>
     </row>
     <row r="22" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
+      <c r="B22" s="65" t="s">
         <v>469</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
     </row>
     <row r="23" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="D23" s="14" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:41" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="31" t="s">
+      <c r="B24" s="29" t="s">
         <v>471</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="C24" s="30" t="s">
         <v>472</v>
       </c>
-      <c r="C24" s="33" t="str">
-        <f>INDEX(A6:A11,MATCH(MAX(B6:B11),B6:B11,0))</f>
+      <c r="D24" s="31" t="str">
+        <f>INDEX(B6:B11,MATCH(MAX(C6:C11),C6:C11,0))</f>
         <v>Mayo</v>
       </c>
     </row>
     <row r="25" spans="1:41" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="31" t="s">
+      <c r="B25" s="29" t="s">
         <v>473</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="C25" s="30" t="s">
         <v>468</v>
       </c>
-      <c r="C25" s="34">
-        <f>MAX(B6:B11)</f>
+      <c r="D25" s="32">
+        <f>MAX(C6:C11)</f>
         <v>15200</v>
       </c>
     </row>
     <row r="26" spans="1:41" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="35" t="s">
+      <c r="B26" s="33" t="s">
         <v>474</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="C26" s="34" t="s">
         <v>475</v>
       </c>
-      <c r="C26" s="37" t="str">
-        <f>INDEX(A6:A11,MATCH(MIN(B6:B11),B6:B11,0))</f>
+      <c r="D26" s="35" t="str">
+        <f>INDEX(B6:B11,MATCH(MIN(C6:C11),C6:C11,0))</f>
         <v>Marzo</v>
       </c>
     </row>
     <row r="27" spans="1:41" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35" t="s">
+      <c r="B27" s="33" t="s">
         <v>476</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="C27" s="34" t="s">
         <v>466</v>
       </c>
-      <c r="C27" s="38">
-        <f>MIN(B6:B11)</f>
+      <c r="D27" s="36">
+        <f>MIN(C6:C11)</f>
         <v>11800</v>
       </c>
     </row>
-    <row r="30" spans="1:41" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:41" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="59"/>
+    </row>
     <row r="32" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
+      <c r="A32" s="60"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -12645,7 +12761,7 @@
       <c r="AO32" s="1"/>
     </row>
     <row r="33" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
+      <c r="A33" s="60"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -12688,7 +12804,7 @@
       <c r="AO33" s="1"/>
     </row>
     <row r="34" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
+      <c r="A34" s="60"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -12731,7 +12847,7 @@
       <c r="AO34" s="1"/>
     </row>
     <row r="35" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
+      <c r="A35" s="60"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -12774,7 +12890,7 @@
       <c r="AO35" s="1"/>
     </row>
     <row r="36" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
+      <c r="A36" s="60"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -12817,7 +12933,7 @@
       <c r="AO36" s="1"/>
     </row>
     <row r="37" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
+      <c r="A37" s="60"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -12860,7 +12976,7 @@
       <c r="AO37" s="1"/>
     </row>
     <row r="38" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1"/>
+      <c r="A38" s="60"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -12903,7 +13019,7 @@
       <c r="AO38" s="1"/>
     </row>
     <row r="39" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
+      <c r="A39" s="60"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -12946,7 +13062,7 @@
       <c r="AO39" s="1"/>
     </row>
     <row r="40" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
+      <c r="A40" s="60"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -12989,7 +13105,7 @@
       <c r="AO40" s="1"/>
     </row>
     <row r="41" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
+      <c r="A41" s="60"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -13032,7 +13148,7 @@
       <c r="AO41" s="1"/>
     </row>
     <row r="42" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
+      <c r="A42" s="60"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -13075,7 +13191,7 @@
       <c r="AO42" s="1"/>
     </row>
     <row r="43" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
+      <c r="A43" s="60"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -13118,7 +13234,7 @@
       <c r="AO43" s="1"/>
     </row>
     <row r="44" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
+      <c r="A44" s="60"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -13161,7 +13277,7 @@
       <c r="AO44" s="1"/>
     </row>
     <row r="45" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
+      <c r="A45" s="60"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -13204,7 +13320,7 @@
       <c r="AO45" s="1"/>
     </row>
     <row r="46" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
+      <c r="A46" s="60"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -13247,7 +13363,7 @@
       <c r="AO46" s="1"/>
     </row>
     <row r="47" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
+      <c r="A47" s="60"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -13290,7 +13406,7 @@
       <c r="AO47" s="1"/>
     </row>
     <row r="48" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
+      <c r="A48" s="60"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -13333,7 +13449,7 @@
       <c r="AO48" s="1"/>
     </row>
     <row r="49" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
+      <c r="A49" s="60"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -13376,7 +13492,7 @@
       <c r="AO49" s="1"/>
     </row>
     <row r="50" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="1"/>
+      <c r="A50" s="60"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -13419,7 +13535,7 @@
       <c r="AO50" s="1"/>
     </row>
     <row r="51" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
+      <c r="A51" s="60"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -13462,7 +13578,7 @@
       <c r="AO51" s="1"/>
     </row>
     <row r="52" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="1"/>
+      <c r="A52" s="60"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -13505,7 +13621,7 @@
       <c r="AO52" s="1"/>
     </row>
     <row r="53" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="1"/>
+      <c r="A53" s="60"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -13548,7 +13664,7 @@
       <c r="AO53" s="1"/>
     </row>
     <row r="54" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="1"/>
+      <c r="A54" s="60"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -13591,7 +13707,7 @@
       <c r="AO54" s="1"/>
     </row>
     <row r="55" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="1"/>
+      <c r="A55" s="60"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -13634,7 +13750,7 @@
       <c r="AO55" s="1"/>
     </row>
     <row r="56" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="1"/>
+      <c r="A56" s="60"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -13677,7 +13793,7 @@
       <c r="AO56" s="1"/>
     </row>
     <row r="57" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="1"/>
+      <c r="A57" s="60"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -13720,7 +13836,7 @@
       <c r="AO57" s="1"/>
     </row>
     <row r="58" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="1"/>
+      <c r="A58" s="60"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -13763,7 +13879,7 @@
       <c r="AO58" s="1"/>
     </row>
     <row r="59" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="1"/>
+      <c r="A59" s="60"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -13806,7 +13922,7 @@
       <c r="AO59" s="1"/>
     </row>
     <row r="60" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="1"/>
+      <c r="A60" s="60"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -13849,7 +13965,7 @@
       <c r="AO60" s="1"/>
     </row>
     <row r="61" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="1"/>
+      <c r="A61" s="60"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -13892,7 +14008,7 @@
       <c r="AO61" s="1"/>
     </row>
     <row r="62" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="1"/>
+      <c r="A62" s="60"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -13935,7 +14051,7 @@
       <c r="AO62" s="1"/>
     </row>
     <row r="63" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="1"/>
+      <c r="A63" s="60"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -13978,7 +14094,7 @@
       <c r="AO63" s="1"/>
     </row>
     <row r="64" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="1"/>
+      <c r="A64" s="60"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -14021,7 +14137,7 @@
       <c r="AO64" s="1"/>
     </row>
     <row r="65" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="1"/>
+      <c r="A65" s="60"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -14064,7 +14180,7 @@
       <c r="AO65" s="1"/>
     </row>
     <row r="66" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="1"/>
+      <c r="A66" s="60"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -14107,7 +14223,7 @@
       <c r="AO66" s="1"/>
     </row>
     <row r="67" spans="1:41" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="1"/>
+      <c r="A67" s="60"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -14151,9 +14267,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B22:D22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -14163,726 +14279,727 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F67"/>
+  <dimension ref="B2:G67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="20.1640625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="48" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="11"/>
+    <col min="1" max="1" width="10.83203125" style="11"/>
+    <col min="2" max="2" width="15.6640625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="22.5" style="43" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="2:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="F2" s="39"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
+      <c r="G2" s="37"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="55" t="s">
         <v>575</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="C4" s="55" t="s">
         <v>576</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="D4" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="E4" s="55" t="s">
         <v>577</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="F4" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="G4" s="56" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="38" t="s">
         <v>578</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="C5" s="38" t="s">
         <v>579</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="D5" s="39" t="s">
         <v>580</v>
       </c>
-      <c r="D5" s="44">
+      <c r="E5" s="40">
         <v>3</v>
       </c>
-      <c r="E5" s="45">
+      <c r="F5" s="41">
         <v>2699.97</v>
       </c>
-      <c r="F5" s="46">
-        <f>E5-(D5*VLOOKUP(B5,$A$31:$E$40,5,FALSE))</f>
+      <c r="G5" s="42">
+        <f>F5-(E5*VLOOKUP(C5,$B$31:$F$40,5,FALSE))</f>
         <v>839.9699999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="42" t="s">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="38" t="s">
         <v>581</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="C6" s="38" t="s">
         <v>582</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="D6" s="39" t="s">
         <v>583</v>
       </c>
-      <c r="D6" s="44">
+      <c r="E6" s="40">
         <v>5</v>
       </c>
-      <c r="E6" s="45">
+      <c r="F6" s="41">
         <v>227.5</v>
       </c>
-      <c r="F6" s="46">
-        <f t="shared" ref="F6:F24" si="0">E6-(D6*VLOOKUP(B6,$A$31:$E$40,5,FALSE))</f>
+      <c r="G6" s="42">
+        <f t="shared" ref="G6:G24" si="0">F6-(E6*VLOOKUP(C6,$B$31:$F$40,5,FALSE))</f>
         <v>137.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="42" t="s">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="38" t="s">
         <v>584</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="C7" s="38" t="s">
         <v>585</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="D7" s="39" t="s">
         <v>586</v>
       </c>
-      <c r="D7" s="44">
+      <c r="E7" s="40">
         <v>2</v>
       </c>
-      <c r="E7" s="45">
+      <c r="F7" s="41">
         <v>239.98</v>
       </c>
-      <c r="F7" s="46">
+      <c r="G7" s="42">
         <f t="shared" si="0"/>
         <v>95.97999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="s">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="C8" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="D8" s="39" t="s">
         <v>589</v>
       </c>
-      <c r="D8" s="44">
+      <c r="E8" s="40">
         <v>4</v>
       </c>
-      <c r="E8" s="45">
+      <c r="F8" s="41">
         <v>51.96</v>
       </c>
-      <c r="F8" s="46">
+      <c r="G8" s="42">
         <f t="shared" si="0"/>
         <v>37.96</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="42" t="s">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="38" t="s">
         <v>590</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="C9" s="38" t="s">
         <v>591</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="D9" s="39" t="s">
         <v>592</v>
       </c>
-      <c r="D9" s="44">
+      <c r="E9" s="40">
         <v>1</v>
       </c>
-      <c r="E9" s="45">
+      <c r="F9" s="41">
         <v>899.99</v>
       </c>
-      <c r="F9" s="46">
+      <c r="G9" s="42">
         <f t="shared" si="0"/>
         <v>319.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="42" t="s">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="38" t="s">
         <v>593</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="C10" s="38" t="s">
         <v>579</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="D10" s="39" t="s">
         <v>594</v>
       </c>
-      <c r="D10" s="44">
+      <c r="E10" s="40">
         <v>2</v>
       </c>
-      <c r="E10" s="45">
+      <c r="F10" s="41">
         <v>1799.98</v>
       </c>
-      <c r="F10" s="46">
+      <c r="G10" s="42">
         <f t="shared" si="0"/>
         <v>559.98</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
         <v>595</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="C11" s="38" t="s">
         <v>596</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="D11" s="39" t="s">
         <v>597</v>
       </c>
-      <c r="D11" s="44">
+      <c r="E11" s="40">
         <v>6</v>
       </c>
-      <c r="E11" s="45">
+      <c r="F11" s="41">
         <v>77.94</v>
       </c>
-      <c r="F11" s="46">
+      <c r="G11" s="42">
         <f t="shared" si="0"/>
         <v>52.739999999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="42" t="s">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="38" t="s">
         <v>598</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="C12" s="38" t="s">
         <v>582</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="D12" s="39" t="s">
         <v>599</v>
       </c>
-      <c r="D12" s="44">
+      <c r="E12" s="40">
         <v>3</v>
       </c>
-      <c r="E12" s="45">
+      <c r="F12" s="41">
         <v>136.5</v>
       </c>
-      <c r="F12" s="46">
+      <c r="G12" s="42">
         <f t="shared" si="0"/>
         <v>82.5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="42" t="s">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="38" t="s">
         <v>600</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="C13" s="38" t="s">
         <v>601</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="D13" s="39" t="s">
         <v>602</v>
       </c>
-      <c r="D13" s="44">
+      <c r="E13" s="40">
         <v>2</v>
       </c>
-      <c r="E13" s="45">
+      <c r="F13" s="41">
         <v>319.98</v>
       </c>
-      <c r="F13" s="46">
+      <c r="G13" s="42">
         <f t="shared" si="0"/>
         <v>189.98000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="42" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="38" t="s">
         <v>603</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="C14" s="38" t="s">
         <v>585</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="D14" s="39" t="s">
         <v>604</v>
       </c>
-      <c r="D14" s="44">
+      <c r="E14" s="40">
         <v>3</v>
       </c>
-      <c r="E14" s="45">
+      <c r="F14" s="41">
         <v>359.97</v>
       </c>
-      <c r="F14" s="46">
+      <c r="G14" s="42">
         <f t="shared" si="0"/>
         <v>143.97000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="42" t="s">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="38" t="s">
         <v>605</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="C15" s="38" t="s">
         <v>606</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="D15" s="39" t="s">
         <v>607</v>
       </c>
-      <c r="D15" s="44">
+      <c r="E15" s="40">
         <v>5</v>
       </c>
-      <c r="E15" s="45">
+      <c r="F15" s="41">
         <v>124.95</v>
       </c>
-      <c r="F15" s="46">
+      <c r="G15" s="42">
         <f t="shared" si="0"/>
         <v>94.95</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="42" t="s">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="38" t="s">
         <v>608</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="C16" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="D16" s="39" t="s">
         <v>609</v>
       </c>
-      <c r="D16" s="44">
+      <c r="E16" s="40">
         <v>8</v>
       </c>
-      <c r="E16" s="45">
+      <c r="F16" s="41">
         <v>103.92</v>
       </c>
-      <c r="F16" s="46">
+      <c r="G16" s="42">
         <f t="shared" si="0"/>
         <v>75.92</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="42" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="38" t="s">
         <v>610</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="C17" s="38" t="s">
         <v>591</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="D17" s="39" t="s">
         <v>611</v>
       </c>
-      <c r="D17" s="44">
+      <c r="E17" s="40">
         <v>2</v>
       </c>
-      <c r="E17" s="45">
+      <c r="F17" s="41">
         <v>1799.98</v>
       </c>
-      <c r="F17" s="46">
+      <c r="G17" s="42">
         <f t="shared" si="0"/>
         <v>639.98</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="42" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="38" t="s">
         <v>612</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="C18" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="D18" s="39" t="s">
         <v>614</v>
       </c>
-      <c r="D18" s="44">
+      <c r="E18" s="40">
         <v>4</v>
       </c>
-      <c r="E18" s="45">
+      <c r="F18" s="41">
         <v>239.96</v>
       </c>
-      <c r="F18" s="46">
+      <c r="G18" s="42">
         <f t="shared" si="0"/>
         <v>139.96</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="42" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="38" t="s">
         <v>615</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="C19" s="38" t="s">
         <v>616</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="D19" s="39" t="s">
         <v>617</v>
       </c>
-      <c r="D19" s="44">
+      <c r="E19" s="40">
         <v>1</v>
       </c>
-      <c r="E19" s="45">
+      <c r="F19" s="41">
         <v>449.99</v>
       </c>
-      <c r="F19" s="46">
+      <c r="G19" s="42">
         <f t="shared" si="0"/>
         <v>139.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="38" t="s">
         <v>618</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="C20" s="38" t="s">
         <v>596</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="D20" s="39" t="s">
         <v>619</v>
       </c>
-      <c r="D20" s="44">
+      <c r="E20" s="40">
         <v>3</v>
       </c>
-      <c r="E20" s="45">
+      <c r="F20" s="41">
         <v>38.97</v>
       </c>
-      <c r="F20" s="46">
+      <c r="G20" s="42">
         <f t="shared" si="0"/>
         <v>26.369999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="42" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="38" t="s">
         <v>620</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="C21" s="38" t="s">
         <v>579</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="D21" s="39" t="s">
         <v>621</v>
       </c>
-      <c r="D21" s="44">
+      <c r="E21" s="40">
         <v>1</v>
       </c>
-      <c r="E21" s="45">
+      <c r="F21" s="41">
         <v>899.99</v>
       </c>
-      <c r="F21" s="46">
+      <c r="G21" s="42">
         <f t="shared" si="0"/>
         <v>279.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="42" t="s">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="38" t="s">
         <v>622</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="C22" s="38" t="s">
         <v>601</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="D22" s="39" t="s">
         <v>623</v>
       </c>
-      <c r="D22" s="44">
+      <c r="E22" s="40">
         <v>5</v>
       </c>
-      <c r="E22" s="45">
+      <c r="F22" s="41">
         <v>799.95</v>
       </c>
-      <c r="F22" s="46">
+      <c r="G22" s="42">
         <f t="shared" si="0"/>
         <v>474.95000000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="42" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="38" t="s">
         <v>624</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="C23" s="38" t="s">
         <v>606</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="D23" s="39" t="s">
         <v>625</v>
       </c>
-      <c r="D23" s="44">
+      <c r="E23" s="40">
         <v>2</v>
       </c>
-      <c r="E23" s="45">
+      <c r="F23" s="41">
         <v>49.98</v>
       </c>
-      <c r="F23" s="46">
+      <c r="G23" s="42">
         <f t="shared" si="0"/>
         <v>37.979999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="42" t="s">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="38" t="s">
         <v>626</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="C24" s="38" t="s">
         <v>616</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="D24" s="39" t="s">
         <v>627</v>
       </c>
-      <c r="D24" s="44">
+      <c r="E24" s="40">
         <v>3</v>
       </c>
-      <c r="E24" s="45">
+      <c r="F24" s="41">
         <v>1349.97</v>
       </c>
-      <c r="F24" s="46">
+      <c r="G24" s="42">
         <f t="shared" si="0"/>
         <v>419.97</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12" t="s">
+    <row r="28" spans="2:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="F28" s="39"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="47" t="s">
+      <c r="G28" s="37"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="57" t="s">
         <v>576</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="C30" s="57" t="s">
         <v>629</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="D30" s="57" t="s">
         <v>479</v>
       </c>
-      <c r="D30" s="47" t="s">
+      <c r="E30" s="57" t="s">
         <v>630</v>
       </c>
-      <c r="E30" s="47" t="s">
+      <c r="F30" s="57" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="49" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="44" t="s">
         <v>579</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="C31" s="44" t="s">
         <v>493</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="D31" s="44" t="s">
         <v>632</v>
       </c>
-      <c r="D31" s="50">
+      <c r="E31" s="45">
         <v>899.99</v>
       </c>
-      <c r="E31" s="50">
+      <c r="F31" s="45">
         <v>620</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="49" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="44" t="s">
         <v>582</v>
       </c>
-      <c r="B32" s="49" t="s">
+      <c r="C32" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="D32" s="44" t="s">
         <v>633</v>
       </c>
-      <c r="D32" s="50">
+      <c r="E32" s="45">
         <v>45.5</v>
       </c>
-      <c r="E32" s="50">
+      <c r="F32" s="45">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="49" t="s">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33" s="44" t="s">
         <v>585</v>
       </c>
-      <c r="B33" s="49" t="s">
+      <c r="C33" s="44" t="s">
         <v>495</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="D33" s="44" t="s">
         <v>632</v>
       </c>
-      <c r="D33" s="50">
+      <c r="E33" s="45">
         <v>119.99</v>
       </c>
-      <c r="E33" s="50">
+      <c r="F33" s="45">
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="49" t="s">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B34" s="44" t="s">
         <v>588</v>
       </c>
-      <c r="B34" s="49" t="s">
+      <c r="C34" s="44" t="s">
         <v>508</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="D34" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="50">
+      <c r="E34" s="45">
         <v>12.99</v>
       </c>
-      <c r="E34" s="50">
+      <c r="F34" s="45">
         <v>3.5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="49" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="44" t="s">
         <v>591</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="C35" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="D35" s="44" t="s">
         <v>632</v>
       </c>
-      <c r="D35" s="50">
+      <c r="E35" s="45">
         <v>899.99</v>
       </c>
-      <c r="E35" s="50">
+      <c r="F35" s="45">
         <v>580</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="49" t="s">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="44" t="s">
         <v>596</v>
       </c>
-      <c r="B36" s="49" t="s">
+      <c r="C36" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="C36" s="49" t="s">
+      <c r="D36" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="50">
+      <c r="E36" s="45">
         <v>12.99</v>
       </c>
-      <c r="E36" s="50">
+      <c r="F36" s="45">
         <v>4.2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="49" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="44" t="s">
         <v>601</v>
       </c>
-      <c r="B37" s="49" t="s">
+      <c r="C37" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="D37" s="44" t="s">
         <v>633</v>
       </c>
-      <c r="D37" s="50">
+      <c r="E37" s="45">
         <v>159.99</v>
       </c>
-      <c r="E37" s="50">
+      <c r="F37" s="45">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="49" t="s">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="44" t="s">
         <v>606</v>
       </c>
-      <c r="B38" s="49" t="s">
+      <c r="C38" s="44" t="s">
         <v>503</v>
       </c>
-      <c r="C38" s="49" t="s">
+      <c r="D38" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="D38" s="50">
+      <c r="E38" s="45">
         <v>24.99</v>
       </c>
-      <c r="E38" s="50">
+      <c r="F38" s="45">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="49" t="s">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="44" t="s">
         <v>613</v>
       </c>
-      <c r="B39" s="49" t="s">
+      <c r="C39" s="44" t="s">
         <v>542</v>
       </c>
-      <c r="C39" s="49" t="s">
+      <c r="D39" s="44" t="s">
         <v>633</v>
       </c>
-      <c r="D39" s="50">
+      <c r="E39" s="45">
         <v>59.99</v>
       </c>
-      <c r="E39" s="50">
+      <c r="F39" s="45">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="49" t="s">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="44" t="s">
         <v>616</v>
       </c>
-      <c r="B40" s="49" t="s">
+      <c r="C40" s="44" t="s">
         <v>634</v>
       </c>
-      <c r="C40" s="49" t="s">
+      <c r="D40" s="44" t="s">
         <v>632</v>
       </c>
-      <c r="D40" s="50">
+      <c r="E40" s="45">
         <v>449.99</v>
       </c>
-      <c r="E40" s="50">
+      <c r="F40" s="45">
         <v>310</v>
       </c>
     </row>
-    <row r="44" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="12" t="s">
+    <row r="44" spans="2:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="F44" s="39"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="11" t="s">
+      <c r="G44" s="37"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B46" s="11" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="11" t="s">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B47" s="11" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" s="11" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B52" s="2" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="1"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B53" s="1"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B54" s="2" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55" s="2" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B56" s="2" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B60" s="2" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="1"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B61" s="1"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="12" t="s">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B66" s="12" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="11" t="s">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B67" s="11" t="s">
         <v>647</v>
       </c>
     </row>

--- a/Prueba-01-Analisis-Datos/solucion.xlsx
+++ b/Prueba-01-Analisis-Datos/solucion.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="600" yWindow="460" windowWidth="28200" windowHeight="17540" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Material de apoyo - Prueba " sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="673">
   <si>
     <t>Fecha</t>
   </si>
@@ -1956,21 +1956,6 @@
     <t>Tabla 2: Productos (ID_Producto, Nombre, Categoría, Precio_Unitario)</t>
   </si>
   <si>
-    <t>¿Cómo relacionarías estas tablas en Power Pivot?</t>
-  </si>
-  <si>
-    <t>El problema es que en Ventas solo guardas el código del producto (P001, P002...), no el nombre ni el precio. Power Pivot necesita saber cómo unirlas.</t>
-  </si>
-  <si>
-    <t>El proceso en 3 pasos simples</t>
-  </si>
-  <si>
-    <t>¿Qué logras con eso?</t>
-  </si>
-  <si>
-    <t>A partir de ese momento puedes crear medidas que usen datos de las dos tablas al mismo tiempo, como calcular el margen de ganancia multiplicando la cantidad vendida (que está en Ventas) por el precio (que está en Productos).</t>
-  </si>
-  <si>
     <t>Margen de Ganancia</t>
   </si>
   <si>
@@ -2080,180 +2065,6 @@
   </si>
   <si>
     <t>Quitar Duplicados (Datos)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Ventas </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">— cada vez que alguien compró algo </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Productos</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> — la ficha de cada producto </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1. Cargar las tablas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Seleccionas tu tabla de Ventas → clic en </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Agregar al modelo de datos"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Repites con Productos.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. Ir al diagrama</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Dentro de Power Pivot, cambias a </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Vista de diagrama"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> y ves las dos tablas como cajitas.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3. Arrastrar el campo en común</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Tomas ID_Producto de la tabla Ventas y lo arrastras encima de ID_Producto de Productos. Se dibuja una línea entre las dos tablas. Eso es todo.</t>
-    </r>
-  </si>
-  <si>
-    <t>Que Power Pivot sepa que cuando ve P001 en Ventas, debe ir a buscar el nombre, la categoría y el precio a la tabla Productos. Sin necesidad de escribir ningún VLOOKUP.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Medida DAX </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(referencia, ya que mi Mac no tiene Power Pivot):</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Margen de Ganancia =</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> DIVIDE(SUM(Ventas[Monto]) - SUM(Ventas[Cantidad] * Productos[Costo_Unitario]), SUM(Ventas[Monto]))</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -2555,7 +2366,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2564,6 +2375,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2739,13 +2552,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="10">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="8" builtinId="8" hidden="1"/>
     <cellStyle name="Hipervínculo visitado" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Hipervínculo visitado" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Hipervínculo visitado" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="9" builtinId="9" hidden="1"/>
     <cellStyle name="Moneda [0]" xfId="7" builtinId="7"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -3175,11 +2990,11 @@
         </c:hiLowLines>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="2128685584"/>
-        <c:axId val="2128691632"/>
+        <c:axId val="2110981280"/>
+        <c:axId val="2110987328"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2128685584"/>
+        <c:axId val="2110981280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3254,7 +3069,7 @@
             <a:endParaRPr lang="es-ES_tradnl"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2128691632"/>
+        <c:crossAx val="2110987328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3262,7 +3077,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2128691632"/>
+        <c:axId val="2110987328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3345,7 +3160,7 @@
             <a:endParaRPr lang="es-ES_tradnl"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2128685584"/>
+        <c:crossAx val="2110981280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="4000.0"/>
@@ -3449,6 +3264,346 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6540500" cy="7581900"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CuadroTexto 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10490200" y="533400"/>
+          <a:ext cx="6540500" cy="7581900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1800" b="1"/>
+            <a:t>¿Cómo relacionarías estas tablas en Power Pivot?</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+          </a:br>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Ventas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> — cada vez que alguien compró algo.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Productos</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> — la ficha de cada producto.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+          </a:br>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>El problema es que en </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Ventas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> solo guardas el código del producto (P001, P002...), no el nombre ni el precio. Power Pivot necesita saber cómo unirlas.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+          </a:br>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>El proceso en 3 pasos simples</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>1. Cargar las tablas</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>Seleccionas tu tabla de </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Ventas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> → clic en </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>"Agregar al modelo de datos"</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>Repites el proceso con </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Productos</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+          </a:br>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>2. Ir al diagrama</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>Dentro de Power Pivot, cambias a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>"Vista de diagrama"</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> y ves las dos tablas como cajitas.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+          </a:br>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>3. Arrastrar el campo en común</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>Tomas </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>ID_Producto</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> de la tabla </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Ventas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> y lo arrastras encima de </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>ID_Producto</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> de </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Productos</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>Se dibuja una línea entre las dos tablas. Eso es todo.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+          </a:br>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>¿Qué logras con eso?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>Power Pivot sabe que, cuando ve </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>P001</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t> en Ventas, debe ir a buscar el nombre, la categoría y el precio a la tabla </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Productos</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>, sin necesidad de escribir ningún </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>VLOOKUP</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>A partir de ese momento puedes crear medidas que usen datos de las dos tablas al mismo tiempo, como calcular el margen de ganancia multiplicando la cantidad vendida (que está en </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Ventas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>) por el precio (que está en </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Productos</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>).</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+          </a:br>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" b="1"/>
+            <a:t>Medida DAX</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400" i="1"/>
+            <a:t>Referencia, ya que mi Mac no tiene Power Pivot:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES_tradnl" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES_tradnl" sz="1400"/>
+            <a:t>Margen de Ganancia = DIVIDE( SUM(Ventas[Monto]) - SUM(Ventas[Cantidad] * Productos[Costo_Unitario]), SUM(Ventas[Monto]) )  </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -3537,10 +3692,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Tabla7" displayName="Tabla7" ref="B13:E17" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="B13:E17"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="#" dataDxfId="3"/>
-    <tableColumn id="2" name="Problema Detectado" dataDxfId="2"/>
-    <tableColumn id="3" name="Técnica de Excel" dataDxfId="1"/>
-    <tableColumn id="4" name="Resultado" dataDxfId="0"/>
+    <tableColumn id="1" name="#" dataDxfId="1"/>
+    <tableColumn id="2" name="Problema Detectado" dataDxfId="0"/>
+    <tableColumn id="3" name="Técnica de Excel" dataDxfId="3"/>
+    <tableColumn id="4" name="Resultado" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10860,97 +11015,97 @@
     <row r="1" spans="2:5" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="10" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B4" s="11" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="57" x14ac:dyDescent="0.2">
       <c r="B5" s="12" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="38" x14ac:dyDescent="0.2">
       <c r="B6" s="12" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="57" x14ac:dyDescent="0.2">
       <c r="B7" s="12" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="38" x14ac:dyDescent="0.2">
       <c r="B8" s="12" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="2:5" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="10" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12" spans="2:5" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B13" s="15" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>456</v>
@@ -10961,13 +11116,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="38" x14ac:dyDescent="0.2">
@@ -10975,13 +11130,13 @@
         <v>2</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="38" x14ac:dyDescent="0.2">
@@ -10989,13 +11144,13 @@
         <v>3</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="38" x14ac:dyDescent="0.2">
@@ -11003,13 +11158,13 @@
         <v>4</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
     </row>
     <row r="18" spans="2:5" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -14252,7 +14407,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G65"/>
+  <dimension ref="B2:G38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="53"/>
@@ -14262,7 +14417,9 @@
     <col min="5" max="5" width="15.1640625" style="53" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="53" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="60" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="53"/>
+    <col min="8" max="8" width="10.83203125" style="53"/>
+    <col min="9" max="14" width="10.83203125" style="53" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="53"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" s="49" customFormat="1" x14ac:dyDescent="0.25">
@@ -14288,7 +14445,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -14308,7 +14465,7 @@
         <v>2699.97</v>
       </c>
       <c r="G5" s="58">
-        <f>F5-(E5*VLOOKUP(C5,$B$29:$F$38,5,FALSE))</f>
+        <f t="shared" ref="G5:G24" si="0">F5-(E5*VLOOKUP(C5,$B$29:$F$38,5,FALSE))</f>
         <v>839.9699999999998</v>
       </c>
     </row>
@@ -14329,7 +14486,7 @@
         <v>227.5</v>
       </c>
       <c r="G6" s="58">
-        <f t="shared" ref="G6:G24" si="0">F6-(E6*VLOOKUP(C6,$B$29:$F$38,5,FALSE))</f>
+        <f t="shared" si="0"/>
         <v>137.5</v>
       </c>
     </row>
@@ -14802,7 +14959,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="61" t="s">
         <v>591</v>
       </c>
@@ -14819,7 +14976,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="61" t="s">
         <v>596</v>
       </c>
@@ -14836,7 +14993,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="61" t="s">
         <v>601</v>
       </c>
@@ -14853,7 +15010,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="61" t="s">
         <v>606</v>
       </c>
@@ -14870,7 +15027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="61" t="s">
         <v>613</v>
       </c>
@@ -14887,7 +15044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="61" t="s">
         <v>616</v>
       </c>
@@ -14904,79 +15061,8 @@
         <v>310</v>
       </c>
     </row>
-    <row r="42" spans="2:7" s="49" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="49" t="s">
-        <v>636</v>
-      </c>
-      <c r="G42" s="50"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="53" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="53" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="53" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="18" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="20"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="18" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="18" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="18" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="18" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="20"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="20" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" s="20" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="49" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" s="53" t="s">
-        <v>685</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>